--- a/output/pdf_financials_xlsx/BRE.xlsx
+++ b/output/pdf_financials_xlsx/BRE.xlsx
@@ -2041,34 +2041,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.052</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.645</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.102</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.458</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.339</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.202</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.217</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.419</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.743</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.458</v>
       </c>
     </row>
     <row r="35">
@@ -2115,34 +2115,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.052</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.645</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.102</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.458</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.339</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.217</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.419</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.743</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.458</v>
       </c>
     </row>
     <row r="37">
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.217</v>
+        <v>0.165</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.822</v>
+        <v>0.177</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.259</v>
+        <v>0.157</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.642</v>
+        <v>0.184</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.15</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.691</v>
+        <v>0.489</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.635</v>
+        <v>0.418</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.331</v>
+        <v>1.912</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.859</v>
+        <v>1.116</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.642</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="49">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">

--- a/output/pdf_financials_xlsx/BRE.xlsx
+++ b/output/pdf_financials_xlsx/BRE.xlsx
@@ -4503,31 +4503,31 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>10.828</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>9.583</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.137</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>7.705</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>7.631</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>7.624</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>7.429</v>
       </c>
       <c r="K100" s="1" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">

--- a/output/pdf_financials_xlsx/BRE.xlsx
+++ b/output/pdf_financials_xlsx/BRE.xlsx
@@ -5127,19 +5127,19 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-5.998</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-18.15</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-9.429</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-10.137</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-10.792</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -15554,7 +15554,11 @@
           <t>Deferred income tax expense 7</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -16252,7 +16256,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>-0.991</v>
       </c>
@@ -16554,7 +16562,11 @@
           <t>Purchase of intangible assets 6</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -17642,7 +17654,11 @@
           <t>Deferred income tax expense / (recovery) 8</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -17958,7 +17974,11 @@
           <t>Purchase of intangible assets 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E197" s="5" t="n">
         <v>-5.998</v>
       </c>
@@ -20310,7 +20330,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E234" s="5" t="n">
         <v>-0.991</v>
       </c>
